--- a/artfynd/A 28063-2024 artfynd.xlsx
+++ b/artfynd/A 28063-2024 artfynd.xlsx
@@ -3098,10 +3098,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118437172</v>
+        <v>118438270</v>
       </c>
       <c r="B25" t="n">
-        <v>95394</v>
+        <v>57290</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3114,34 +3114,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>725088</v>
+        <v>725422</v>
       </c>
       <c r="R25" t="n">
-        <v>7347447</v>
+        <v>7347639</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3174,6 +3182,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3200,10 +3213,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118437090</v>
+        <v>118437172</v>
       </c>
       <c r="B26" t="n">
-        <v>91070</v>
+        <v>95394</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3212,25 +3225,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>760</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3240,10 +3253,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>725035</v>
+        <v>725088</v>
       </c>
       <c r="R26" t="n">
-        <v>7347407</v>
+        <v>7347447</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3302,10 +3315,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118435677</v>
+        <v>118437090</v>
       </c>
       <c r="B27" t="n">
-        <v>97013</v>
+        <v>91070</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3314,25 +3327,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220250</v>
+        <v>760</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3342,10 +3355,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>724670</v>
+        <v>725035</v>
       </c>
       <c r="R27" t="n">
-        <v>7347029</v>
+        <v>7347407</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3404,10 +3417,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118438270</v>
+        <v>118435677</v>
       </c>
       <c r="B28" t="n">
-        <v>57290</v>
+        <v>97013</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3416,46 +3429,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220250</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>725422</v>
+        <v>724670</v>
       </c>
       <c r="R28" t="n">
-        <v>7347639</v>
+        <v>7347029</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3488,11 +3493,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 28063-2024 artfynd.xlsx
+++ b/artfynd/A 28063-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118437913</v>
+        <v>118438270</v>
       </c>
       <c r="B2" t="n">
-        <v>79469</v>
+        <v>57290</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>725296</v>
+        <v>725422</v>
       </c>
       <c r="R2" t="n">
-        <v>7347499</v>
+        <v>7347639</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +759,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118438683</v>
+        <v>118437172</v>
       </c>
       <c r="B3" t="n">
-        <v>91070</v>
+        <v>95394</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +802,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>760</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>725356</v>
+        <v>725088</v>
       </c>
       <c r="R3" t="n">
-        <v>7347834</v>
+        <v>7347447</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118437738</v>
+        <v>118437090</v>
       </c>
       <c r="B4" t="n">
-        <v>57290</v>
+        <v>91070</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,46 +904,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>725226</v>
+        <v>725035</v>
       </c>
       <c r="R4" t="n">
-        <v>7347443</v>
+        <v>7347407</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,11 +968,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118436559</v>
+        <v>118435771</v>
       </c>
       <c r="B5" t="n">
-        <v>57443</v>
+        <v>79601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,25 +1006,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1034,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>724912</v>
+        <v>724691</v>
       </c>
       <c r="R5" t="n">
-        <v>7347322</v>
+        <v>7347031</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118438460</v>
+        <v>118435677</v>
       </c>
       <c r="B6" t="n">
-        <v>97763</v>
+        <v>97013</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1112,34 +1112,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>220250</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>725382</v>
+        <v>724670</v>
       </c>
       <c r="R6" t="n">
-        <v>7347780</v>
+        <v>7347029</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118436580</v>
+        <v>118437738</v>
       </c>
       <c r="B7" t="n">
         <v>57290</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>724906</v>
+        <v>725226</v>
       </c>
       <c r="R7" t="n">
-        <v>7347324</v>
+        <v>7347443</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Skalad bark</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118438175</v>
+        <v>118437503</v>
       </c>
       <c r="B8" t="n">
-        <v>57290</v>
+        <v>91070</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1325,46 +1325,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>725419</v>
+        <v>725117</v>
       </c>
       <c r="R8" t="n">
-        <v>7347583</v>
+        <v>7347440</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,11 +1389,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1428,10 +1415,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118435160</v>
+        <v>118435348</v>
       </c>
       <c r="B9" t="n">
-        <v>90522</v>
+        <v>104925</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,38 +1427,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>221725</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kåbdalis, Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>724423</v>
+        <v>724547</v>
       </c>
       <c r="R9" t="n">
-        <v>7346944</v>
+        <v>7346987</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,10 +1517,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118436132</v>
+        <v>118435160</v>
       </c>
       <c r="B10" t="n">
-        <v>90504</v>
+        <v>90522</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,34 +1533,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Kåbdalis, Lu lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>724797</v>
+        <v>724423</v>
       </c>
       <c r="R10" t="n">
-        <v>7347080</v>
+        <v>7346944</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1632,10 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118449717</v>
+        <v>118436253</v>
       </c>
       <c r="B11" t="n">
-        <v>57401</v>
+        <v>57290</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,20 +1631,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1665,29 +1652,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kåbdalis, Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>724884</v>
+        <v>724814</v>
       </c>
       <c r="R11" t="n">
-        <v>7347246</v>
+        <v>7347160</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,6 +1703,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1746,10 +1734,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118435204</v>
+        <v>118438683</v>
       </c>
       <c r="B12" t="n">
-        <v>97867</v>
+        <v>91070</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1758,38 +1746,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>760</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>724427</v>
+        <v>725356</v>
       </c>
       <c r="R12" t="n">
-        <v>7346951</v>
+        <v>7347834</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,10 +1836,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118436253</v>
+        <v>118438668</v>
       </c>
       <c r="B13" t="n">
-        <v>57290</v>
+        <v>79566</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1864,42 +1852,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>724814</v>
+        <v>725356</v>
       </c>
       <c r="R13" t="n">
-        <v>7347160</v>
+        <v>7347836</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,11 +1912,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1963,10 +1938,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118435348</v>
+        <v>118438175</v>
       </c>
       <c r="B14" t="n">
-        <v>104925</v>
+        <v>57290</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1975,38 +1950,46 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>724547</v>
+        <v>725419</v>
       </c>
       <c r="R14" t="n">
-        <v>7346987</v>
+        <v>7347583</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,6 +2022,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2065,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118435771</v>
+        <v>118435456</v>
       </c>
       <c r="B15" t="n">
-        <v>79601</v>
+        <v>90500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2077,25 +2065,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2105,10 +2093,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>724691</v>
+        <v>724603</v>
       </c>
       <c r="R15" t="n">
-        <v>7347031</v>
+        <v>7347014</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2167,10 +2155,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118435178</v>
+        <v>118436404</v>
       </c>
       <c r="B16" t="n">
-        <v>74596</v>
+        <v>90899</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2179,25 +2167,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>4217</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2207,10 +2195,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>724419</v>
+        <v>724835</v>
       </c>
       <c r="R16" t="n">
-        <v>7346964</v>
+        <v>7347232</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2269,10 +2257,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118438668</v>
+        <v>118435178</v>
       </c>
       <c r="B17" t="n">
-        <v>79566</v>
+        <v>74596</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2285,34 +2273,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>725356</v>
+        <v>724419</v>
       </c>
       <c r="R17" t="n">
-        <v>7347836</v>
+        <v>7346964</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2473,10 +2461,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118436404</v>
+        <v>118439016</v>
       </c>
       <c r="B19" t="n">
-        <v>90899</v>
+        <v>104925</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2489,34 +2477,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4217</v>
+        <v>221725</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Ridok (Ridok), Lu lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>724835</v>
+        <v>724986</v>
       </c>
       <c r="R19" t="n">
-        <v>7347232</v>
+        <v>7347817</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2575,10 +2563,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118436227</v>
+        <v>118449717</v>
       </c>
       <c r="B20" t="n">
-        <v>57290</v>
+        <v>57401</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2587,20 +2575,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2608,25 +2596,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Kåbdalis, Lu lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>724805</v>
+        <v>724884</v>
       </c>
       <c r="R20" t="n">
-        <v>7347151</v>
+        <v>7347246</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2659,11 +2651,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2690,10 +2677,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118436292</v>
+        <v>118437614</v>
       </c>
       <c r="B21" t="n">
-        <v>91070</v>
+        <v>79594</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2702,25 +2689,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>760</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2730,10 +2717,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>724826</v>
+        <v>725186</v>
       </c>
       <c r="R21" t="n">
-        <v>7347173</v>
+        <v>7347430</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2792,10 +2779,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118437503</v>
+        <v>118436559</v>
       </c>
       <c r="B22" t="n">
-        <v>91070</v>
+        <v>57443</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2804,25 +2791,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>760</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2832,10 +2819,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>725117</v>
+        <v>724912</v>
       </c>
       <c r="R22" t="n">
-        <v>7347440</v>
+        <v>7347322</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2894,10 +2881,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118436150</v>
+        <v>118436132</v>
       </c>
       <c r="B23" t="n">
-        <v>95394</v>
+        <v>90504</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2910,21 +2897,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2934,10 +2921,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>724791</v>
+        <v>724797</v>
       </c>
       <c r="R23" t="n">
-        <v>7347082</v>
+        <v>7347080</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2996,10 +2983,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118439016</v>
+        <v>118437024</v>
       </c>
       <c r="B24" t="n">
-        <v>104925</v>
+        <v>82263</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3008,38 +2995,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221725</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ridok (Ridok), Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>724986</v>
+        <v>724964</v>
       </c>
       <c r="R24" t="n">
-        <v>7347817</v>
+        <v>7347376</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3098,10 +3085,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118438270</v>
+        <v>118436397</v>
       </c>
       <c r="B25" t="n">
-        <v>57290</v>
+        <v>90504</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3114,42 +3101,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>725422</v>
+        <v>724827</v>
       </c>
       <c r="R25" t="n">
-        <v>7347639</v>
+        <v>7347216</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3182,11 +3161,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3213,10 +3187,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118437172</v>
+        <v>118437913</v>
       </c>
       <c r="B26" t="n">
-        <v>95394</v>
+        <v>79469</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3225,38 +3199,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>6456</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>725088</v>
+        <v>725296</v>
       </c>
       <c r="R26" t="n">
-        <v>7347447</v>
+        <v>7347499</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3315,7 +3289,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118437090</v>
+        <v>118436292</v>
       </c>
       <c r="B27" t="n">
         <v>91070</v>
@@ -3355,10 +3329,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>725035</v>
+        <v>724826</v>
       </c>
       <c r="R27" t="n">
-        <v>7347407</v>
+        <v>7347173</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3417,10 +3391,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118435677</v>
+        <v>118438448</v>
       </c>
       <c r="B28" t="n">
-        <v>97013</v>
+        <v>78484</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3429,38 +3403,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220250</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>724670</v>
+        <v>725381</v>
       </c>
       <c r="R28" t="n">
-        <v>7347029</v>
+        <v>7347772</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3493,6 +3472,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3519,10 +3503,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118438448</v>
+        <v>118436150</v>
       </c>
       <c r="B29" t="n">
-        <v>78484</v>
+        <v>95394</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3535,39 +3519,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>725381</v>
+        <v>724791</v>
       </c>
       <c r="R29" t="n">
-        <v>7347772</v>
+        <v>7347082</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3600,11 +3579,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3631,10 +3605,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118437614</v>
+        <v>118438214</v>
       </c>
       <c r="B30" t="n">
-        <v>79594</v>
+        <v>57290</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3643,38 +3617,46 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>725186</v>
+        <v>725417</v>
       </c>
       <c r="R30" t="n">
-        <v>7347430</v>
+        <v>7347614</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3707,6 +3689,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3733,10 +3720,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118437024</v>
+        <v>118436580</v>
       </c>
       <c r="B31" t="n">
-        <v>82263</v>
+        <v>57290</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3749,34 +3736,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>724964</v>
+        <v>724906</v>
       </c>
       <c r="R31" t="n">
-        <v>7347376</v>
+        <v>7347324</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3809,6 +3804,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3835,10 +3835,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118435456</v>
+        <v>118436227</v>
       </c>
       <c r="B32" t="n">
-        <v>90500</v>
+        <v>57290</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3851,34 +3851,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>724603</v>
+        <v>724805</v>
       </c>
       <c r="R32" t="n">
-        <v>7347014</v>
+        <v>7347151</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3911,6 +3919,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3937,10 +3950,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118436397</v>
+        <v>118438460</v>
       </c>
       <c r="B33" t="n">
-        <v>90504</v>
+        <v>97763</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3949,38 +3962,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>724827</v>
+        <v>725382</v>
       </c>
       <c r="R33" t="n">
-        <v>7347216</v>
+        <v>7347780</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4039,10 +4052,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118438214</v>
+        <v>118436973</v>
       </c>
       <c r="B34" t="n">
-        <v>57290</v>
+        <v>90504</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4055,42 +4068,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>725417</v>
+        <v>724993</v>
       </c>
       <c r="R34" t="n">
-        <v>7347614</v>
+        <v>7347363</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4123,11 +4128,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4154,10 +4154,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118436973</v>
+        <v>118435204</v>
       </c>
       <c r="B35" t="n">
-        <v>90504</v>
+        <v>97867</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4166,25 +4166,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4194,10 +4194,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>724993</v>
+        <v>724427</v>
       </c>
       <c r="R35" t="n">
-        <v>7347363</v>
+        <v>7346951</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 28063-2024 artfynd.xlsx
+++ b/artfynd/A 28063-2024 artfynd.xlsx
@@ -1096,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118435677</v>
+        <v>118437738</v>
       </c>
       <c r="B6" t="n">
-        <v>97013</v>
+        <v>57290</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,38 +1108,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220250</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>724670</v>
+        <v>725226</v>
       </c>
       <c r="R6" t="n">
-        <v>7347029</v>
+        <v>7347443</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,6 +1180,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118437738</v>
+        <v>118435677</v>
       </c>
       <c r="B7" t="n">
-        <v>57290</v>
+        <v>97013</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,46 +1223,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220250</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>725226</v>
+        <v>724670</v>
       </c>
       <c r="R7" t="n">
-        <v>7347443</v>
+        <v>7347029</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1282,11 +1287,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1938,10 +1938,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118438175</v>
+        <v>118436404</v>
       </c>
       <c r="B14" t="n">
-        <v>57290</v>
+        <v>90899</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,46 +1950,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>4217</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>725419</v>
+        <v>724835</v>
       </c>
       <c r="R14" t="n">
-        <v>7347583</v>
+        <v>7347232</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2022,11 +2014,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2053,10 +2040,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118435456</v>
+        <v>118435178</v>
       </c>
       <c r="B15" t="n">
-        <v>90500</v>
+        <v>74596</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,21 +2056,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2093,10 +2080,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>724603</v>
+        <v>724419</v>
       </c>
       <c r="R15" t="n">
-        <v>7347014</v>
+        <v>7346964</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2155,10 +2142,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118436404</v>
+        <v>118435309</v>
       </c>
       <c r="B16" t="n">
-        <v>90899</v>
+        <v>79594</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2171,21 +2158,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4217</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2195,10 +2182,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>724835</v>
+        <v>724506</v>
       </c>
       <c r="R16" t="n">
-        <v>7347232</v>
+        <v>7346988</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2257,10 +2244,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118435178</v>
+        <v>118438175</v>
       </c>
       <c r="B17" t="n">
-        <v>74596</v>
+        <v>57290</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2273,34 +2260,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>724419</v>
+        <v>725419</v>
       </c>
       <c r="R17" t="n">
-        <v>7346964</v>
+        <v>7347583</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2333,6 +2328,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2359,10 +2359,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118435309</v>
+        <v>118439016</v>
       </c>
       <c r="B18" t="n">
-        <v>79594</v>
+        <v>104925</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2375,34 +2375,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>221725</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Ridok (Ridok), Lu lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>724506</v>
+        <v>724986</v>
       </c>
       <c r="R18" t="n">
-        <v>7346988</v>
+        <v>7347817</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2461,10 +2461,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118439016</v>
+        <v>118435456</v>
       </c>
       <c r="B19" t="n">
-        <v>104925</v>
+        <v>90500</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2473,38 +2473,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221725</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ridok (Ridok), Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>724986</v>
+        <v>724603</v>
       </c>
       <c r="R19" t="n">
-        <v>7347817</v>
+        <v>7347014</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 28063-2024 artfynd.xlsx
+++ b/artfynd/A 28063-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118438270</v>
+        <v>118437913</v>
       </c>
       <c r="B2" t="n">
-        <v>57290</v>
+        <v>79469</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>725422</v>
+        <v>725296</v>
       </c>
       <c r="R2" t="n">
-        <v>7347639</v>
+        <v>7347499</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118437172</v>
+        <v>118435309</v>
       </c>
       <c r="B3" t="n">
-        <v>95394</v>
+        <v>79594</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -830,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>725088</v>
+        <v>724506</v>
       </c>
       <c r="R3" t="n">
-        <v>7347447</v>
+        <v>7346988</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118437090</v>
+        <v>118436227</v>
       </c>
       <c r="B4" t="n">
-        <v>91070</v>
+        <v>57290</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,38 +891,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>725035</v>
+        <v>724805</v>
       </c>
       <c r="R4" t="n">
-        <v>7347407</v>
+        <v>7347151</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,6 +963,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118435771</v>
+        <v>118438175</v>
       </c>
       <c r="B5" t="n">
-        <v>79601</v>
+        <v>57290</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,38 +1006,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>724691</v>
+        <v>725419</v>
       </c>
       <c r="R5" t="n">
-        <v>7347031</v>
+        <v>7347583</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,6 +1078,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,7 +1109,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118437738</v>
+        <v>118438270</v>
       </c>
       <c r="B6" t="n">
         <v>57290</v>
@@ -1140,14 +1153,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>725226</v>
+        <v>725422</v>
       </c>
       <c r="R6" t="n">
-        <v>7347443</v>
+        <v>7347639</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,7 +1197,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1211,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118435677</v>
+        <v>118436559</v>
       </c>
       <c r="B7" t="n">
-        <v>97013</v>
+        <v>57443</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1223,25 +1236,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220250</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1251,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>724670</v>
+        <v>724912</v>
       </c>
       <c r="R7" t="n">
-        <v>7347029</v>
+        <v>7347322</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1313,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118437503</v>
+        <v>118435456</v>
       </c>
       <c r="B8" t="n">
-        <v>91070</v>
+        <v>90500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1325,25 +1338,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>760</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1353,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>725117</v>
+        <v>724603</v>
       </c>
       <c r="R8" t="n">
-        <v>7347440</v>
+        <v>7347014</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118435348</v>
+        <v>118436150</v>
       </c>
       <c r="B9" t="n">
-        <v>104925</v>
+        <v>95394</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1427,25 +1440,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221725</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>724547</v>
+        <v>724791</v>
       </c>
       <c r="R9" t="n">
-        <v>7346987</v>
+        <v>7347082</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,10 +1530,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118435160</v>
+        <v>118437090</v>
       </c>
       <c r="B10" t="n">
-        <v>90522</v>
+        <v>91070</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1529,38 +1542,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>760</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kåbdalis, Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>724423</v>
+        <v>725035</v>
       </c>
       <c r="R10" t="n">
-        <v>7346944</v>
+        <v>7347407</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1619,7 +1632,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118436253</v>
+        <v>118438214</v>
       </c>
       <c r="B11" t="n">
         <v>57290</v>
@@ -1657,20 +1670,20 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>724814</v>
+        <v>725417</v>
       </c>
       <c r="R11" t="n">
-        <v>7347160</v>
+        <v>7347614</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1707,7 +1720,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1734,10 +1747,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118438683</v>
+        <v>118436397</v>
       </c>
       <c r="B12" t="n">
-        <v>91070</v>
+        <v>90504</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,38 +1759,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>760</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>725356</v>
+        <v>724827</v>
       </c>
       <c r="R12" t="n">
-        <v>7347834</v>
+        <v>7347216</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1836,10 +1849,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118438668</v>
+        <v>118435677</v>
       </c>
       <c r="B13" t="n">
-        <v>79566</v>
+        <v>97013</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,38 +1861,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>220250</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>725356</v>
+        <v>724670</v>
       </c>
       <c r="R13" t="n">
-        <v>7347836</v>
+        <v>7347029</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2040,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118435178</v>
+        <v>118435160</v>
       </c>
       <c r="B15" t="n">
-        <v>74596</v>
+        <v>90522</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2056,34 +2069,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Kåbdalis, Lu lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>724419</v>
+        <v>724423</v>
       </c>
       <c r="R15" t="n">
-        <v>7346964</v>
+        <v>7346944</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2142,10 +2155,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118435309</v>
+        <v>118438668</v>
       </c>
       <c r="B16" t="n">
-        <v>79594</v>
+        <v>79566</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2154,38 +2167,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>724506</v>
+        <v>725356</v>
       </c>
       <c r="R16" t="n">
-        <v>7346988</v>
+        <v>7347836</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2244,10 +2257,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118438175</v>
+        <v>118435178</v>
       </c>
       <c r="B17" t="n">
-        <v>57290</v>
+        <v>74596</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2260,42 +2273,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>725419</v>
+        <v>724419</v>
       </c>
       <c r="R17" t="n">
-        <v>7347583</v>
+        <v>7346964</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2328,11 +2333,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2359,10 +2359,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118439016</v>
+        <v>118436292</v>
       </c>
       <c r="B18" t="n">
-        <v>104925</v>
+        <v>91070</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2371,38 +2371,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221725</v>
+        <v>760</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ridok (Ridok), Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>724986</v>
+        <v>724826</v>
       </c>
       <c r="R18" t="n">
-        <v>7347817</v>
+        <v>7347173</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2461,10 +2461,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118435456</v>
+        <v>118438448</v>
       </c>
       <c r="B19" t="n">
-        <v>90500</v>
+        <v>78484</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2477,34 +2477,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>724603</v>
+        <v>725381</v>
       </c>
       <c r="R19" t="n">
-        <v>7347014</v>
+        <v>7347772</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2537,6 +2542,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2563,10 +2573,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118449717</v>
+        <v>118437024</v>
       </c>
       <c r="B20" t="n">
-        <v>57401</v>
+        <v>82263</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2575,50 +2585,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103031</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kåbdalis, Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>724884</v>
+        <v>724964</v>
       </c>
       <c r="R20" t="n">
-        <v>7347246</v>
+        <v>7347376</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2677,10 +2675,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118437614</v>
+        <v>118437738</v>
       </c>
       <c r="B21" t="n">
-        <v>79594</v>
+        <v>57290</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2689,38 +2687,46 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>725186</v>
+        <v>725226</v>
       </c>
       <c r="R21" t="n">
-        <v>7347430</v>
+        <v>7347443</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2753,6 +2759,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2779,10 +2790,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118436559</v>
+        <v>118449717</v>
       </c>
       <c r="B22" t="n">
-        <v>57443</v>
+        <v>57401</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2791,38 +2802,50 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>103031</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Kåbdalis, Lu lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>724912</v>
+        <v>724884</v>
       </c>
       <c r="R22" t="n">
-        <v>7347322</v>
+        <v>7347246</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,10 +2904,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118436132</v>
+        <v>118435204</v>
       </c>
       <c r="B23" t="n">
-        <v>90504</v>
+        <v>97867</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2893,25 +2916,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2921,10 +2944,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>724797</v>
+        <v>724427</v>
       </c>
       <c r="R23" t="n">
-        <v>7347080</v>
+        <v>7346951</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2983,10 +3006,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118437024</v>
+        <v>118436132</v>
       </c>
       <c r="B24" t="n">
-        <v>82263</v>
+        <v>90504</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2999,21 +3022,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3023,10 +3046,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>724964</v>
+        <v>724797</v>
       </c>
       <c r="R24" t="n">
-        <v>7347376</v>
+        <v>7347080</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3085,10 +3108,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118436397</v>
+        <v>118437172</v>
       </c>
       <c r="B25" t="n">
-        <v>90504</v>
+        <v>95394</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3101,21 +3124,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3125,10 +3148,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>724827</v>
+        <v>725088</v>
       </c>
       <c r="R25" t="n">
-        <v>7347216</v>
+        <v>7347447</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3187,10 +3210,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118437913</v>
+        <v>118436253</v>
       </c>
       <c r="B26" t="n">
-        <v>79469</v>
+        <v>57290</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3199,38 +3222,46 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>725296</v>
+        <v>724814</v>
       </c>
       <c r="R26" t="n">
-        <v>7347499</v>
+        <v>7347160</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3263,6 +3294,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3289,10 +3325,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118436292</v>
+        <v>118436580</v>
       </c>
       <c r="B27" t="n">
-        <v>91070</v>
+        <v>57290</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3301,38 +3337,46 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>724826</v>
+        <v>724906</v>
       </c>
       <c r="R27" t="n">
-        <v>7347173</v>
+        <v>7347324</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3365,6 +3409,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3391,10 +3440,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118438448</v>
+        <v>118435348</v>
       </c>
       <c r="B28" t="n">
-        <v>78484</v>
+        <v>104925</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3403,43 +3452,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>725381</v>
+        <v>724547</v>
       </c>
       <c r="R28" t="n">
-        <v>7347772</v>
+        <v>7346987</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3472,11 +3516,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3503,10 +3542,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118436150</v>
+        <v>118439016</v>
       </c>
       <c r="B29" t="n">
-        <v>95394</v>
+        <v>104925</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3515,38 +3554,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>221725</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Ridok (Ridok), Lu lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>724791</v>
+        <v>724986</v>
       </c>
       <c r="R29" t="n">
-        <v>7347082</v>
+        <v>7347817</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3605,10 +3644,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118438214</v>
+        <v>118438460</v>
       </c>
       <c r="B30" t="n">
-        <v>57290</v>
+        <v>97763</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3617,46 +3656,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>725417</v>
+        <v>725382</v>
       </c>
       <c r="R30" t="n">
-        <v>7347614</v>
+        <v>7347780</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3689,11 +3720,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3720,10 +3746,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118436580</v>
+        <v>118437503</v>
       </c>
       <c r="B31" t="n">
-        <v>57290</v>
+        <v>91070</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3732,46 +3758,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>724906</v>
+        <v>725117</v>
       </c>
       <c r="R31" t="n">
-        <v>7347324</v>
+        <v>7347440</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3804,11 +3822,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3835,10 +3848,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118436227</v>
+        <v>118436973</v>
       </c>
       <c r="B32" t="n">
-        <v>57290</v>
+        <v>90504</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3851,42 +3864,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>724805</v>
+        <v>724993</v>
       </c>
       <c r="R32" t="n">
-        <v>7347151</v>
+        <v>7347363</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3919,11 +3924,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3950,10 +3950,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118438460</v>
+        <v>118438683</v>
       </c>
       <c r="B33" t="n">
-        <v>97763</v>
+        <v>91070</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3962,25 +3962,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219790</v>
+        <v>760</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3990,10 +3990,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>725382</v>
+        <v>725356</v>
       </c>
       <c r="R33" t="n">
-        <v>7347780</v>
+        <v>7347834</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4052,10 +4052,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118436973</v>
+        <v>118435771</v>
       </c>
       <c r="B34" t="n">
-        <v>90504</v>
+        <v>79601</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4064,25 +4064,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4092,10 +4092,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>724993</v>
+        <v>724691</v>
       </c>
       <c r="R34" t="n">
-        <v>7347363</v>
+        <v>7347031</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4154,10 +4154,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118435204</v>
+        <v>118437614</v>
       </c>
       <c r="B35" t="n">
-        <v>97867</v>
+        <v>79594</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4170,21 +4170,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4194,10 +4194,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>724427</v>
+        <v>725186</v>
       </c>
       <c r="R35" t="n">
-        <v>7346951</v>
+        <v>7347430</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 28063-2024 artfynd.xlsx
+++ b/artfynd/A 28063-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118437913</v>
+        <v>118436253</v>
       </c>
       <c r="B2" t="n">
-        <v>79469</v>
+        <v>57290</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>725296</v>
+        <v>724814</v>
       </c>
       <c r="R2" t="n">
-        <v>7347499</v>
+        <v>7347160</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +759,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118435309</v>
+        <v>118436973</v>
       </c>
       <c r="B3" t="n">
-        <v>79594</v>
+        <v>90511</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +802,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>724506</v>
+        <v>724993</v>
       </c>
       <c r="R3" t="n">
-        <v>7346988</v>
+        <v>7347363</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118436227</v>
+        <v>118435771</v>
       </c>
       <c r="B4" t="n">
-        <v>57290</v>
+        <v>79608</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,46 +904,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>724805</v>
+        <v>724691</v>
       </c>
       <c r="R4" t="n">
-        <v>7347151</v>
+        <v>7347031</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,11 +968,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118438175</v>
+        <v>118435309</v>
       </c>
       <c r="B5" t="n">
-        <v>57290</v>
+        <v>79601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,46 +1006,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>725419</v>
+        <v>724506</v>
       </c>
       <c r="R5" t="n">
-        <v>7347583</v>
+        <v>7346988</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,11 +1070,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118438270</v>
+        <v>118437614</v>
       </c>
       <c r="B6" t="n">
-        <v>57290</v>
+        <v>79601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,46 +1108,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>725422</v>
+        <v>725186</v>
       </c>
       <c r="R6" t="n">
-        <v>7347639</v>
+        <v>7347430</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,11 +1172,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,10 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118436559</v>
+        <v>118436292</v>
       </c>
       <c r="B7" t="n">
-        <v>57443</v>
+        <v>91077</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,25 +1210,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>760</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>724912</v>
+        <v>724826</v>
       </c>
       <c r="R7" t="n">
-        <v>7347322</v>
+        <v>7347173</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1326,10 +1300,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118435456</v>
+        <v>118435178</v>
       </c>
       <c r="B8" t="n">
-        <v>90500</v>
+        <v>74603</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,21 +1316,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1366,10 +1340,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>724603</v>
+        <v>724419</v>
       </c>
       <c r="R8" t="n">
-        <v>7347014</v>
+        <v>7346964</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1428,10 +1402,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118436150</v>
+        <v>118435160</v>
       </c>
       <c r="B9" t="n">
-        <v>95394</v>
+        <v>90529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,34 +1418,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Kåbdalis, Lu lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>724791</v>
+        <v>724423</v>
       </c>
       <c r="R9" t="n">
-        <v>7347082</v>
+        <v>7346944</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,10 +1504,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118437090</v>
+        <v>118437738</v>
       </c>
       <c r="B10" t="n">
-        <v>91070</v>
+        <v>57290</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,38 +1516,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>725035</v>
+        <v>725226</v>
       </c>
       <c r="R10" t="n">
-        <v>7347407</v>
+        <v>7347443</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,6 +1588,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1632,10 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118438214</v>
+        <v>118437913</v>
       </c>
       <c r="B11" t="n">
-        <v>57290</v>
+        <v>79476</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,46 +1631,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>725417</v>
+        <v>725296</v>
       </c>
       <c r="R11" t="n">
-        <v>7347614</v>
+        <v>7347499</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1716,11 +1695,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1747,10 +1721,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118436397</v>
+        <v>118449717</v>
       </c>
       <c r="B12" t="n">
-        <v>90504</v>
+        <v>57401</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1759,38 +1733,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Kåbdalis, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>724827</v>
+        <v>724884</v>
       </c>
       <c r="R12" t="n">
-        <v>7347216</v>
+        <v>7347246</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,10 +1835,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118435677</v>
+        <v>118436580</v>
       </c>
       <c r="B13" t="n">
-        <v>97013</v>
+        <v>57290</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1861,38 +1847,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220250</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>724670</v>
+        <v>724906</v>
       </c>
       <c r="R13" t="n">
-        <v>7347029</v>
+        <v>7347324</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1925,6 +1919,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1951,10 +1950,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118436404</v>
+        <v>118435677</v>
       </c>
       <c r="B14" t="n">
-        <v>90899</v>
+        <v>97020</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1967,21 +1966,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4217</v>
+        <v>220250</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1991,10 +1990,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>724835</v>
+        <v>724670</v>
       </c>
       <c r="R14" t="n">
-        <v>7347232</v>
+        <v>7347029</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2052,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118435160</v>
+        <v>118436132</v>
       </c>
       <c r="B15" t="n">
-        <v>90522</v>
+        <v>90511</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,34 +2068,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kåbdalis, Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>724423</v>
+        <v>724797</v>
       </c>
       <c r="R15" t="n">
-        <v>7346944</v>
+        <v>7347080</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2155,10 +2154,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118438668</v>
+        <v>118438270</v>
       </c>
       <c r="B16" t="n">
-        <v>79566</v>
+        <v>57290</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2171,34 +2170,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>725356</v>
+        <v>725422</v>
       </c>
       <c r="R16" t="n">
-        <v>7347836</v>
+        <v>7347639</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2231,6 +2238,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2257,10 +2269,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118435178</v>
+        <v>118437090</v>
       </c>
       <c r="B17" t="n">
-        <v>74596</v>
+        <v>91077</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2269,25 +2281,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>760</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2297,10 +2309,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>724419</v>
+        <v>725035</v>
       </c>
       <c r="R17" t="n">
-        <v>7346964</v>
+        <v>7347407</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2359,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118436292</v>
+        <v>118436397</v>
       </c>
       <c r="B18" t="n">
-        <v>91070</v>
+        <v>90511</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2371,25 +2383,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>760</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2399,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>724826</v>
+        <v>724827</v>
       </c>
       <c r="R18" t="n">
-        <v>7347173</v>
+        <v>7347216</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2461,10 +2473,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118438448</v>
+        <v>118436404</v>
       </c>
       <c r="B19" t="n">
-        <v>78484</v>
+        <v>90906</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2473,43 +2485,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>725381</v>
+        <v>724835</v>
       </c>
       <c r="R19" t="n">
-        <v>7347772</v>
+        <v>7347232</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2542,11 +2549,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2573,10 +2575,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118437024</v>
+        <v>118438683</v>
       </c>
       <c r="B20" t="n">
-        <v>82263</v>
+        <v>91077</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2585,38 +2587,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>760</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>724964</v>
+        <v>725356</v>
       </c>
       <c r="R20" t="n">
-        <v>7347376</v>
+        <v>7347834</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2675,10 +2677,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118437738</v>
+        <v>118435456</v>
       </c>
       <c r="B21" t="n">
-        <v>57290</v>
+        <v>90507</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2691,42 +2693,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>725226</v>
+        <v>724603</v>
       </c>
       <c r="R21" t="n">
-        <v>7347443</v>
+        <v>7347014</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2759,11 +2753,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2790,10 +2779,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118449717</v>
+        <v>118436227</v>
       </c>
       <c r="B22" t="n">
-        <v>57401</v>
+        <v>57290</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2802,20 +2791,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2823,29 +2812,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kåbdalis, Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>724884</v>
+        <v>724805</v>
       </c>
       <c r="R22" t="n">
-        <v>7347246</v>
+        <v>7347151</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2878,6 +2863,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,7 +2897,7 @@
         <v>118435204</v>
       </c>
       <c r="B23" t="n">
-        <v>97867</v>
+        <v>97874</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3006,10 +2996,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118436132</v>
+        <v>118435348</v>
       </c>
       <c r="B24" t="n">
-        <v>90504</v>
+        <v>104932</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3018,25 +3008,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>221725</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3046,10 +3036,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>724797</v>
+        <v>724547</v>
       </c>
       <c r="R24" t="n">
-        <v>7347080</v>
+        <v>7346987</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3108,10 +3098,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118437172</v>
+        <v>118439016</v>
       </c>
       <c r="B25" t="n">
-        <v>95394</v>
+        <v>104932</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3120,38 +3110,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>221725</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Ridok (Ridok), Lu lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>725088</v>
+        <v>724986</v>
       </c>
       <c r="R25" t="n">
-        <v>7347447</v>
+        <v>7347817</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3210,7 +3200,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118436253</v>
+        <v>118438175</v>
       </c>
       <c r="B26" t="n">
         <v>57290</v>
@@ -3248,20 +3238,20 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>724814</v>
+        <v>725419</v>
       </c>
       <c r="R26" t="n">
-        <v>7347160</v>
+        <v>7347583</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3298,7 +3288,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3325,7 +3315,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118436580</v>
+        <v>118438214</v>
       </c>
       <c r="B27" t="n">
         <v>57290</v>
@@ -3363,20 +3353,20 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>724906</v>
+        <v>725417</v>
       </c>
       <c r="R27" t="n">
-        <v>7347324</v>
+        <v>7347614</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3413,7 +3403,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Skalad bark</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3440,10 +3430,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118435348</v>
+        <v>118436559</v>
       </c>
       <c r="B28" t="n">
-        <v>104925</v>
+        <v>57443</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3452,25 +3442,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221725</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3480,10 +3470,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>724547</v>
+        <v>724912</v>
       </c>
       <c r="R28" t="n">
-        <v>7346987</v>
+        <v>7347322</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3542,10 +3532,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118439016</v>
+        <v>118437172</v>
       </c>
       <c r="B29" t="n">
-        <v>104925</v>
+        <v>95401</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3554,38 +3544,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221725</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ridok (Ridok), Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>724986</v>
+        <v>725088</v>
       </c>
       <c r="R29" t="n">
-        <v>7347817</v>
+        <v>7347447</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3644,10 +3634,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118438460</v>
+        <v>118436150</v>
       </c>
       <c r="B30" t="n">
-        <v>97763</v>
+        <v>95401</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3656,38 +3646,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219790</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>725382</v>
+        <v>724791</v>
       </c>
       <c r="R30" t="n">
-        <v>7347780</v>
+        <v>7347082</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3746,10 +3736,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118437503</v>
+        <v>118438448</v>
       </c>
       <c r="B31" t="n">
-        <v>91070</v>
+        <v>78491</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3758,38 +3748,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>725117</v>
+        <v>725381</v>
       </c>
       <c r="R31" t="n">
-        <v>7347440</v>
+        <v>7347772</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3822,6 +3817,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3848,10 +3848,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118436973</v>
+        <v>118438460</v>
       </c>
       <c r="B32" t="n">
-        <v>90504</v>
+        <v>97770</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3860,38 +3860,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>724993</v>
+        <v>725382</v>
       </c>
       <c r="R32" t="n">
-        <v>7347363</v>
+        <v>7347780</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3950,10 +3950,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118438683</v>
+        <v>118438668</v>
       </c>
       <c r="B33" t="n">
-        <v>91070</v>
+        <v>79573</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3962,25 +3962,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3993,7 +3993,7 @@
         <v>725356</v>
       </c>
       <c r="R33" t="n">
-        <v>7347834</v>
+        <v>7347836</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4052,10 +4052,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118435771</v>
+        <v>118437503</v>
       </c>
       <c r="B34" t="n">
-        <v>79601</v>
+        <v>91077</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4064,25 +4064,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6464</v>
+        <v>760</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4092,10 +4092,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>724691</v>
+        <v>725117</v>
       </c>
       <c r="R34" t="n">
-        <v>7347031</v>
+        <v>7347440</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4154,10 +4154,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118437614</v>
+        <v>118437024</v>
       </c>
       <c r="B35" t="n">
-        <v>79594</v>
+        <v>82270</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4166,25 +4166,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4194,10 +4194,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>725186</v>
+        <v>724964</v>
       </c>
       <c r="R35" t="n">
-        <v>7347430</v>
+        <v>7347376</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 28063-2024 artfynd.xlsx
+++ b/artfynd/A 28063-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118436253</v>
+        <v>118436973</v>
       </c>
       <c r="B2" t="n">
-        <v>57290</v>
+        <v>90511</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>724814</v>
+        <v>724993</v>
       </c>
       <c r="R2" t="n">
-        <v>7347160</v>
+        <v>7347363</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118436973</v>
+        <v>118436253</v>
       </c>
       <c r="B3" t="n">
-        <v>90511</v>
+        <v>57290</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,34 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>724993</v>
+        <v>724814</v>
       </c>
       <c r="R3" t="n">
-        <v>7347363</v>
+        <v>7347160</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,6 +861,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 28063-2024 artfynd.xlsx
+++ b/artfynd/A 28063-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118436973</v>
+        <v>118436150</v>
       </c>
       <c r="B2" t="n">
-        <v>90511</v>
+        <v>95401</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>724993</v>
+        <v>724791</v>
       </c>
       <c r="R2" t="n">
-        <v>7347363</v>
+        <v>7347082</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118436253</v>
+        <v>118435178</v>
       </c>
       <c r="B3" t="n">
-        <v>57290</v>
+        <v>74603</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,42 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>724814</v>
+        <v>724419</v>
       </c>
       <c r="R3" t="n">
-        <v>7347160</v>
+        <v>7346964</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118435771</v>
+        <v>118436559</v>
       </c>
       <c r="B4" t="n">
-        <v>79608</v>
+        <v>57443</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>724691</v>
+        <v>724912</v>
       </c>
       <c r="R4" t="n">
-        <v>7347031</v>
+        <v>7347322</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118435309</v>
+        <v>118436292</v>
       </c>
       <c r="B5" t="n">
-        <v>79601</v>
+        <v>91077</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>760</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1034,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>724506</v>
+        <v>724826</v>
       </c>
       <c r="R5" t="n">
-        <v>7346988</v>
+        <v>7347173</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118437614</v>
+        <v>118436132</v>
       </c>
       <c r="B6" t="n">
-        <v>79601</v>
+        <v>90511</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1136,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>725186</v>
+        <v>724797</v>
       </c>
       <c r="R6" t="n">
-        <v>7347430</v>
+        <v>7347080</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118436292</v>
+        <v>118435204</v>
       </c>
       <c r="B7" t="n">
-        <v>91077</v>
+        <v>97874</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>760</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1238,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>724826</v>
+        <v>724427</v>
       </c>
       <c r="R7" t="n">
-        <v>7347173</v>
+        <v>7346951</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118435178</v>
+        <v>118438668</v>
       </c>
       <c r="B8" t="n">
-        <v>74603</v>
+        <v>79573</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1316,34 +1303,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>724419</v>
+        <v>725356</v>
       </c>
       <c r="R8" t="n">
-        <v>7346964</v>
+        <v>7347836</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118435160</v>
+        <v>118435771</v>
       </c>
       <c r="B9" t="n">
-        <v>90529</v>
+        <v>79608</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1414,38 +1401,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kåbdalis, Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>724423</v>
+        <v>724691</v>
       </c>
       <c r="R9" t="n">
-        <v>7346944</v>
+        <v>7347031</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118437738</v>
+        <v>118435160</v>
       </c>
       <c r="B10" t="n">
-        <v>57290</v>
+        <v>90529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1520,42 +1507,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Kåbdalis, Lu lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>725226</v>
+        <v>724423</v>
       </c>
       <c r="R10" t="n">
-        <v>7347443</v>
+        <v>7346944</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1588,11 +1567,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1619,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118437913</v>
+        <v>118438270</v>
       </c>
       <c r="B11" t="n">
-        <v>79476</v>
+        <v>57290</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1631,38 +1605,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>725296</v>
+        <v>725422</v>
       </c>
       <c r="R11" t="n">
-        <v>7347499</v>
+        <v>7347639</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,6 +1677,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1721,10 +1708,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118449717</v>
+        <v>118439016</v>
       </c>
       <c r="B12" t="n">
-        <v>57401</v>
+        <v>104932</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1737,46 +1724,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103031</v>
+        <v>221725</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kåbdalis, Lu lm</t>
+          <t>Ridok (Ridok), Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>724884</v>
+        <v>724986</v>
       </c>
       <c r="R12" t="n">
-        <v>7347246</v>
+        <v>7347817</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1835,10 +1810,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118436580</v>
+        <v>118438448</v>
       </c>
       <c r="B13" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1851,42 +1826,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>724906</v>
+        <v>725381</v>
       </c>
       <c r="R13" t="n">
-        <v>7347324</v>
+        <v>7347772</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1923,7 +1895,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Skalad bark</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1950,10 +1922,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118435677</v>
+        <v>118438175</v>
       </c>
       <c r="B14" t="n">
-        <v>97020</v>
+        <v>57290</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1962,38 +1934,46 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220250</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>724670</v>
+        <v>725419</v>
       </c>
       <c r="R14" t="n">
-        <v>7347029</v>
+        <v>7347583</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2026,6 +2006,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2052,10 +2037,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118436132</v>
+        <v>118435348</v>
       </c>
       <c r="B15" t="n">
-        <v>90511</v>
+        <v>104932</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2064,25 +2049,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>221725</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2092,10 +2077,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>724797</v>
+        <v>724547</v>
       </c>
       <c r="R15" t="n">
-        <v>7347080</v>
+        <v>7346987</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2154,10 +2139,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118438270</v>
+        <v>118437172</v>
       </c>
       <c r="B16" t="n">
-        <v>57290</v>
+        <v>95401</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2170,42 +2155,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>725422</v>
+        <v>725088</v>
       </c>
       <c r="R16" t="n">
-        <v>7347639</v>
+        <v>7347447</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2238,11 +2215,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2269,10 +2241,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118437090</v>
+        <v>118435456</v>
       </c>
       <c r="B17" t="n">
-        <v>91077</v>
+        <v>90507</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,25 +2253,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>760</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2309,10 +2281,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>725035</v>
+        <v>724603</v>
       </c>
       <c r="R17" t="n">
-        <v>7347407</v>
+        <v>7347014</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2343,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118436397</v>
+        <v>118436253</v>
       </c>
       <c r="B18" t="n">
-        <v>90511</v>
+        <v>57290</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2387,34 +2359,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>724827</v>
+        <v>724814</v>
       </c>
       <c r="R18" t="n">
-        <v>7347216</v>
+        <v>7347160</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,6 +2427,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2473,10 +2458,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118436404</v>
+        <v>118438460</v>
       </c>
       <c r="B19" t="n">
-        <v>90906</v>
+        <v>97770</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2489,34 +2474,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4217</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>724835</v>
+        <v>725382</v>
       </c>
       <c r="R19" t="n">
-        <v>7347232</v>
+        <v>7347780</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2575,10 +2560,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118438683</v>
+        <v>118437738</v>
       </c>
       <c r="B20" t="n">
-        <v>91077</v>
+        <v>57290</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2587,38 +2572,46 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>725356</v>
+        <v>725226</v>
       </c>
       <c r="R20" t="n">
-        <v>7347834</v>
+        <v>7347443</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2651,6 +2644,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2677,10 +2675,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118435456</v>
+        <v>118436397</v>
       </c>
       <c r="B21" t="n">
-        <v>90507</v>
+        <v>90511</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2693,21 +2691,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2717,10 +2715,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>724603</v>
+        <v>724827</v>
       </c>
       <c r="R21" t="n">
-        <v>7347014</v>
+        <v>7347216</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2779,10 +2777,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118436227</v>
+        <v>118435677</v>
       </c>
       <c r="B22" t="n">
-        <v>57290</v>
+        <v>97020</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2791,46 +2789,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220250</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>724805</v>
+        <v>724670</v>
       </c>
       <c r="R22" t="n">
-        <v>7347151</v>
+        <v>7347029</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2863,11 +2853,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2894,10 +2879,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118435204</v>
+        <v>118437090</v>
       </c>
       <c r="B23" t="n">
-        <v>97874</v>
+        <v>91077</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2906,25 +2891,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>760</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2934,10 +2919,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>724427</v>
+        <v>725035</v>
       </c>
       <c r="R23" t="n">
-        <v>7346951</v>
+        <v>7347407</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2996,10 +2981,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118435348</v>
+        <v>118437913</v>
       </c>
       <c r="B24" t="n">
-        <v>104932</v>
+        <v>79476</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3012,34 +2997,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221725</v>
+        <v>6456</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>724547</v>
+        <v>725296</v>
       </c>
       <c r="R24" t="n">
-        <v>7346987</v>
+        <v>7347499</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3098,10 +3083,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118439016</v>
+        <v>118436580</v>
       </c>
       <c r="B25" t="n">
-        <v>104932</v>
+        <v>57290</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3110,38 +3095,46 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ridok (Ridok), Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>724986</v>
+        <v>724906</v>
       </c>
       <c r="R25" t="n">
-        <v>7347817</v>
+        <v>7347324</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3174,6 +3167,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3200,10 +3198,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118438175</v>
+        <v>118437024</v>
       </c>
       <c r="B26" t="n">
-        <v>57290</v>
+        <v>82270</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3216,42 +3214,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>725419</v>
+        <v>724964</v>
       </c>
       <c r="R26" t="n">
-        <v>7347583</v>
+        <v>7347376</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3284,11 +3274,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3315,10 +3300,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118438214</v>
+        <v>118437614</v>
       </c>
       <c r="B27" t="n">
-        <v>57290</v>
+        <v>79601</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3327,46 +3312,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>725417</v>
+        <v>725186</v>
       </c>
       <c r="R27" t="n">
-        <v>7347614</v>
+        <v>7347430</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3399,11 +3376,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3430,10 +3402,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118436559</v>
+        <v>118438214</v>
       </c>
       <c r="B28" t="n">
-        <v>57443</v>
+        <v>57290</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3446,34 +3418,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>724912</v>
+        <v>725417</v>
       </c>
       <c r="R28" t="n">
-        <v>7347322</v>
+        <v>7347614</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3506,6 +3486,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3532,10 +3517,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118437172</v>
+        <v>118436404</v>
       </c>
       <c r="B29" t="n">
-        <v>95401</v>
+        <v>90906</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3544,25 +3529,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>4217</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3572,10 +3557,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>725088</v>
+        <v>724835</v>
       </c>
       <c r="R29" t="n">
-        <v>7347447</v>
+        <v>7347232</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,10 +3619,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118436150</v>
+        <v>118436227</v>
       </c>
       <c r="B30" t="n">
-        <v>95401</v>
+        <v>57290</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3650,34 +3635,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>724791</v>
+        <v>724805</v>
       </c>
       <c r="R30" t="n">
-        <v>7347082</v>
+        <v>7347151</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3710,6 +3703,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3736,10 +3734,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118438448</v>
+        <v>118435309</v>
       </c>
       <c r="B31" t="n">
-        <v>78491</v>
+        <v>79601</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3748,43 +3746,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>725381</v>
+        <v>724506</v>
       </c>
       <c r="R31" t="n">
-        <v>7347772</v>
+        <v>7346988</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3817,11 +3810,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3848,10 +3836,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118438460</v>
+        <v>118449717</v>
       </c>
       <c r="B32" t="n">
-        <v>97770</v>
+        <v>57401</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3864,34 +3852,46 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219790</v>
+        <v>103031</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
+          <t>Kåbdalis, Lu lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>725382</v>
+        <v>724884</v>
       </c>
       <c r="R32" t="n">
-        <v>7347780</v>
+        <v>7347246</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3950,10 +3950,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118438668</v>
+        <v>118436973</v>
       </c>
       <c r="B33" t="n">
-        <v>79573</v>
+        <v>90511</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3966,34 +3966,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
+          <t>Kåbdalis (Kåbdalis), Lu lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>725356</v>
+        <v>724993</v>
       </c>
       <c r="R33" t="n">
-        <v>7347836</v>
+        <v>7347363</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4154,10 +4154,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118437024</v>
+        <v>118438683</v>
       </c>
       <c r="B35" t="n">
-        <v>82270</v>
+        <v>91077</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4166,38 +4166,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>760</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>724964</v>
+        <v>725356</v>
       </c>
       <c r="R35" t="n">
-        <v>7347376</v>
+        <v>7347834</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 28063-2024 artfynd.xlsx
+++ b/artfynd/A 28063-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118435348</v>
+        <v>118436150</v>
       </c>
       <c r="B2" t="n">
-        <v>104934</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221725</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Kåbdalis, Kåbdalis, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>724547</v>
+        <v>724791</v>
       </c>
       <c r="R2" t="n">
-        <v>7346987</v>
+        <v>7347082</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,50 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118439016</v>
+        <v>118437172</v>
       </c>
       <c r="B3" t="n">
-        <v>104934</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221725</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ridok (Ridok), Lu lm</t>
+          <t>Kåbdalis, Kåbdalis, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>724986</v>
+        <v>725088</v>
       </c>
       <c r="R3" t="n">
-        <v>7347817</v>
+        <v>7347447</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,50 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118435456</v>
+        <v>118436292</v>
       </c>
       <c r="B4" t="n">
-        <v>90509</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Kåbdalis, Kåbdalis, Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>724603</v>
+        <v>724826</v>
       </c>
       <c r="R4" t="n">
-        <v>7347014</v>
+        <v>7347173</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,58 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118438214</v>
+        <v>118437090</v>
       </c>
       <c r="B5" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
+          <t>Kåbdalis, Kåbdalis, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>725417</v>
+        <v>725035</v>
       </c>
       <c r="R5" t="n">
-        <v>7347614</v>
+        <v>7347407</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,50 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118436397</v>
+        <v>118437503</v>
       </c>
       <c r="B6" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Kåbdalis, Kåbdalis, Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>724827</v>
+        <v>725117</v>
       </c>
       <c r="R6" t="n">
-        <v>7347216</v>
+        <v>7347440</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,50 +1160,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118436132</v>
+        <v>118438683</v>
       </c>
       <c r="B7" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Goabddálisvárre, Goabddálisvárre, Lu lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>724797</v>
+        <v>725356</v>
       </c>
       <c r="R7" t="n">
-        <v>7347080</v>
+        <v>7347834</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,50 +1257,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118437913</v>
+        <v>118435456</v>
       </c>
       <c r="B8" t="n">
-        <v>79478</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
+          <t>Kåbdalis, Kåbdalis, Lu lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>725296</v>
+        <v>724603</v>
       </c>
       <c r="R8" t="n">
-        <v>7347499</v>
+        <v>7347014</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,50 +1354,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118437614</v>
+        <v>118436132</v>
       </c>
       <c r="B9" t="n">
-        <v>79603</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Kåbdalis, Kåbdalis, Lu lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>725186</v>
+        <v>724797</v>
       </c>
       <c r="R9" t="n">
-        <v>7347430</v>
+        <v>7347080</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118437738</v>
+        <v>118436397</v>
       </c>
       <c r="B10" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1520,42 +1462,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Kåbdalis, Kåbdalis, Lu lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>725226</v>
+        <v>724827</v>
       </c>
       <c r="R10" t="n">
-        <v>7347443</v>
+        <v>7347216</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1588,11 +1522,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1619,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118438668</v>
+        <v>118436973</v>
       </c>
       <c r="B11" t="n">
-        <v>79575</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1635,34 +1559,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
+          <t>Kåbdalis, Kåbdalis, Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>725356</v>
+        <v>724993</v>
       </c>
       <c r="R11" t="n">
-        <v>7347836</v>
+        <v>7347363</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1721,50 +1645,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118438683</v>
+        <v>118439316</v>
       </c>
       <c r="B12" t="n">
-        <v>91079</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>760</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
+          <t>Kåbdalis, Kåbdalis, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>725356</v>
+        <v>724740</v>
       </c>
       <c r="R12" t="n">
-        <v>7347834</v>
+        <v>7347366</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118435178</v>
+        <v>118437024</v>
       </c>
       <c r="B13" t="n">
-        <v>74605</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,34 +1753,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Kåbdalis, Kåbdalis, Lu lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>724419</v>
+        <v>724964</v>
       </c>
       <c r="R13" t="n">
-        <v>7346964</v>
+        <v>7347376</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1925,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118438270</v>
+        <v>118438668</v>
       </c>
       <c r="B14" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1941,42 +1850,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
+          <t>Goabddálisvárre, Goabddálisvárre, Lu lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>725422</v>
+        <v>725356</v>
       </c>
       <c r="R14" t="n">
-        <v>7347639</v>
+        <v>7347836</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2009,11 +1910,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2040,15 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118438460</v>
+        <v>118436404</v>
       </c>
       <c r="B15" t="n">
-        <v>97772</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,34 +1947,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>4217</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
+          <t>Kåbdalis, Kåbdalis, Lu lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>725382</v>
+        <v>724835</v>
       </c>
       <c r="R15" t="n">
-        <v>7347780</v>
+        <v>7347232</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2142,50 +2033,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118437024</v>
+        <v>118438448</v>
       </c>
       <c r="B16" t="n">
-        <v>82272</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Goabddálisvárre, Goabddálisvárre, Lu lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>724964</v>
+        <v>725381</v>
       </c>
       <c r="R16" t="n">
-        <v>7347376</v>
+        <v>7347772</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2218,6 +2109,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2244,50 +2140,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118436404</v>
+        <v>118435178</v>
       </c>
       <c r="B17" t="n">
-        <v>90908</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4217</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Kåbdalis, Kåbdalis, Lu lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>724835</v>
+        <v>724419</v>
       </c>
       <c r="R17" t="n">
-        <v>7347232</v>
+        <v>7346964</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2346,55 +2237,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118438448</v>
+        <v>118437913</v>
       </c>
       <c r="B18" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
+          <t>Goabddálisvárre, Goabddálisvárre, Lu lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>725381</v>
+        <v>725296</v>
       </c>
       <c r="R18" t="n">
-        <v>7347772</v>
+        <v>7347499</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2427,11 +2308,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2458,58 +2334,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118436253</v>
+        <v>118435309</v>
       </c>
       <c r="B19" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Kåbdalis, Kåbdalis, Lu lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>724814</v>
+        <v>724506</v>
       </c>
       <c r="R19" t="n">
-        <v>7347160</v>
+        <v>7346988</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2542,11 +2405,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2573,50 +2431,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118435160</v>
+        <v>118437614</v>
       </c>
       <c r="B20" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kåbdalis, Lu lm</t>
+          <t>Kåbdalis, Kåbdalis, Lu lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>724423</v>
+        <v>725186</v>
       </c>
       <c r="R20" t="n">
-        <v>7346944</v>
+        <v>7347430</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2675,50 +2528,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118437503</v>
+        <v>118435771</v>
       </c>
       <c r="B21" t="n">
-        <v>91079</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>760</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Kåbdalis, Kåbdalis, Lu lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>725117</v>
+        <v>724691</v>
       </c>
       <c r="R21" t="n">
-        <v>7347440</v>
+        <v>7347031</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2777,15 +2625,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118436580</v>
+        <v>118436062</v>
       </c>
       <c r="B22" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2821,14 +2664,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Kåbdalis, Kåbdalis, Lu lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>724906</v>
+        <v>724810</v>
       </c>
       <c r="R22" t="n">
-        <v>7347324</v>
+        <v>7347031</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2892,50 +2735,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118435204</v>
+        <v>118436227</v>
       </c>
       <c r="B23" t="n">
-        <v>97876</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Kåbdalis, Kåbdalis, Lu lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>724427</v>
+        <v>724805</v>
       </c>
       <c r="R23" t="n">
-        <v>7346951</v>
+        <v>7347151</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2968,6 +2814,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2994,15 +2845,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118437172</v>
+        <v>118436253</v>
       </c>
       <c r="B24" t="n">
-        <v>95403</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3010,34 +2856,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Kåbdalis, Kåbdalis, Lu lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>725088</v>
+        <v>724814</v>
       </c>
       <c r="R24" t="n">
-        <v>7347447</v>
+        <v>7347160</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3070,6 +2924,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3096,50 +2955,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118437090</v>
+        <v>118436580</v>
       </c>
       <c r="B25" t="n">
-        <v>91079</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Kåbdalis, Kåbdalis, Lu lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>725035</v>
+        <v>724906</v>
       </c>
       <c r="R25" t="n">
-        <v>7347407</v>
+        <v>7347324</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3172,6 +3034,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3198,15 +3065,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118436973</v>
+        <v>118437738</v>
       </c>
       <c r="B26" t="n">
-        <v>90513</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3214,34 +3076,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Kåbdalis, Kåbdalis, Lu lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>724993</v>
+        <v>725226</v>
       </c>
       <c r="R26" t="n">
-        <v>7347363</v>
+        <v>7347443</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3274,6 +3144,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3300,50 +3175,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118435309</v>
+        <v>118438175</v>
       </c>
       <c r="B27" t="n">
-        <v>79603</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Goabddálisvárre, Goabddálisvárre, Lu lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>724506</v>
+        <v>725419</v>
       </c>
       <c r="R27" t="n">
-        <v>7346988</v>
+        <v>7347583</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3376,6 +3254,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3402,15 +3285,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118436227</v>
+        <v>118438214</v>
       </c>
       <c r="B28" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3440,20 +3318,20 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Goabddálisvárre, Goabddálisvárre, Lu lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>724805</v>
+        <v>725417</v>
       </c>
       <c r="R28" t="n">
-        <v>7347151</v>
+        <v>7347614</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3490,7 +3368,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3517,50 +3395,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118435677</v>
+        <v>118438270</v>
       </c>
       <c r="B29" t="n">
-        <v>97022</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220250</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Goabddálisvárre, Goabddálisvárre, Lu lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>724670</v>
+        <v>725422</v>
       </c>
       <c r="R29" t="n">
-        <v>7347029</v>
+        <v>7347639</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3593,6 +3474,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Skalad bark</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3619,15 +3505,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118436559</v>
+        <v>118438907</v>
       </c>
       <c r="B30" t="n">
-        <v>57445</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3635,34 +3516,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Ridok, Ridok, Lu lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>724912</v>
+        <v>725120</v>
       </c>
       <c r="R30" t="n">
-        <v>7347322</v>
+        <v>7347891</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3695,6 +3584,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3721,32 +3615,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118449717</v>
+        <v>118439185</v>
       </c>
       <c r="B31" t="n">
-        <v>57403</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3754,29 +3643,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kåbdalis, Lu lm</t>
+          <t>Ridok, Ridok, Lu lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>724884</v>
+        <v>724839</v>
       </c>
       <c r="R31" t="n">
-        <v>7347246</v>
+        <v>7347659</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3809,6 +3694,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3835,50 +3725,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118435771</v>
+        <v>118436559</v>
       </c>
       <c r="B32" t="n">
-        <v>79610</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Kåbdalis, Kåbdalis, Lu lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>724691</v>
+        <v>724912</v>
       </c>
       <c r="R32" t="n">
-        <v>7347031</v>
+        <v>7347322</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3937,15 +3822,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118436150</v>
+        <v>118449717</v>
       </c>
       <c r="B33" t="n">
-        <v>95403</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3953,34 +3833,46 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>103031</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Kåbdalis, Lu lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>724791</v>
+        <v>724884</v>
       </c>
       <c r="R33" t="n">
-        <v>7347082</v>
+        <v>7347246</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4039,50 +3931,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118436292</v>
+        <v>118438460</v>
       </c>
       <c r="B34" t="n">
-        <v>91079</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>760</v>
+        <v>219790</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kåbdalis (Kåbdalis), Lu lm</t>
+          <t>Goabddálisvárre, Goabddálisvárre, Lu lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>724826</v>
+        <v>725382</v>
       </c>
       <c r="R34" t="n">
-        <v>7347173</v>
+        <v>7347780</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4141,58 +4028,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118438175</v>
+        <v>118435677</v>
       </c>
       <c r="B35" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98186</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>220250</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Goabddálisvárre (Goabddálisvárre), Lu lm</t>
+          <t>Kåbdalis, Kåbdalis, Lu lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>725419</v>
+        <v>724670</v>
       </c>
       <c r="R35" t="n">
-        <v>7347583</v>
+        <v>7347029</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4227,11 +4101,6 @@
           <t>2024-07-14</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4253,6 +4122,297 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>118435348</v>
+      </c>
+      <c r="B36" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kåbdalis, Kåbdalis, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>724547</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7346987</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>118439016</v>
+      </c>
+      <c r="B37" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Ridok, Ridok, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>724986</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7347817</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>118435204</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kåbdalis, Kåbdalis, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>724427</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7346951</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28063-2024 artfynd.xlsx
+++ b/artfynd/A 28063-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118436150</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118436292</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118435456</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118436132</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118436397</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118436404</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118435178</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118435309</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118435771</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1655,6 +1705,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118436062</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1765,6 +1820,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118436227</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1875,6 +1935,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118436253</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118436580</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2082,6 +2152,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118436559</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2191,6 +2266,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118449717</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2288,6 +2368,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118435677</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2385,6 +2470,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118435348</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2482,6 +2572,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118435204</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2579,6 +2674,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118437172</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2676,6 +2776,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118437090</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2773,6 +2878,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118437503</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2870,6 +2980,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118438683</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2967,6 +3082,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118436973</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3064,6 +3184,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118439316</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3161,6 +3286,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118437024</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3258,6 +3388,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118438668</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3365,6 +3500,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118438448</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3462,6 +3602,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118437913</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3559,6 +3704,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118437614</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3669,6 +3819,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118437738</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3779,6 +3934,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118438175</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3889,6 +4049,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118438214</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3999,6 +4164,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118438270</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4109,6 +4279,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118438907</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4219,6 +4394,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118439185</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4316,6 +4496,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118438460</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4413,8 +4598,52 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118439016</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>